--- a/artfynd/A 11741-2026 artfynd.xlsx
+++ b/artfynd/A 11741-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103773758</v>
+        <v>103773652</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589915.3439546586</v>
+        <v>589980</v>
       </c>
       <c r="R2" t="n">
-        <v>7045523.379053192</v>
+        <v>7045496</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,14 @@
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,16 +781,11 @@
         <v>103773718</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -829,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589952.0466560017</v>
+        <v>589952</v>
       </c>
       <c r="R3" t="n">
-        <v>7045521.737729901</v>
+        <v>7045522</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +847,9 @@
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,16 +879,11 @@
         <v>103773737</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -942,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589926.0640668069</v>
+        <v>589927</v>
       </c>
       <c r="R4" t="n">
-        <v>7045523.681971718</v>
+        <v>7045523</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +945,9 @@
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,16 +977,11 @@
         <v>103773751</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1055,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589922.2133870608</v>
+        <v>589922</v>
       </c>
       <c r="R5" t="n">
-        <v>7045533.394605778</v>
+        <v>7045533</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1043,9 @@
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,19 +1072,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103773817</v>
+        <v>103773758</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1168,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589973.8431508475</v>
+        <v>589915</v>
       </c>
       <c r="R6" t="n">
-        <v>7045557.175329873</v>
+        <v>7045523</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1141,9 @@
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,19 +1170,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103773652</v>
+        <v>103773807</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1281,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589980.4844632423</v>
+        <v>589969</v>
       </c>
       <c r="R7" t="n">
-        <v>7045496.20218136</v>
+        <v>7045583</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,24 +1239,9 @@
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,19 +1268,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103773807</v>
+        <v>103773817</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1399,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589968.198351611</v>
+        <v>589973</v>
       </c>
       <c r="R8" t="n">
-        <v>7045582.908326765</v>
+        <v>7045557</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,19 +1337,9 @@
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,119 +1363,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>103773702</v>
-      </c>
-      <c r="B9" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Sollefteå, Ång</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>589952.0466560017</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7045521.737729901</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Ådals-Liden</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11741-2026 artfynd.xlsx
+++ b/artfynd/A 11741-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103773652</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103773718</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103773737</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103773751</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103773758</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1265,6 +1295,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103773807</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,8 +1398,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103773817</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>